--- a/output/pdf_financials_xlsx/FYL.xlsx
+++ b/output/pdf_financials_xlsx/FYL.xlsx
@@ -3267,10 +3267,10 @@
         <v>0</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.022589</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>0.097591</v>
       </c>
     </row>
     <row r="92">
@@ -5849,7 +5849,11 @@
           <t>Investment revaluation reserve</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FYL.xlsx
+++ b/output/pdf_financials_xlsx/FYL.xlsx
@@ -816,10 +816,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.015777</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.028036</v>
       </c>
     </row>
     <row r="13">
@@ -1374,10 +1374,10 @@
         <v>-0.107396</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.315815</v>
+        <v>-0.331592</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.433994</v>
+        <v>-0.46203</v>
       </c>
     </row>
     <row r="28">
@@ -1446,10 +1446,10 @@
         <v>-0.107396</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.315815</v>
+        <v>-0.331592</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.433994</v>
+        <v>-0.46203</v>
       </c>
     </row>
     <row r="30">
@@ -5223,7 +5223,11 @@
           <t>Reclamation deposits (Note 5)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -7867,7 +7871,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="n">
         <v>0.0572</v>
       </c>
@@ -9093,7 +9101,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -11783,7 +11795,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">

--- a/output/pdf_financials_xlsx/FYL.xlsx
+++ b/output/pdf_financials_xlsx/FYL.xlsx
@@ -504,25 +504,17 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -540,25 +532,17 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -576,25 +560,17 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -612,25 +588,17 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.030611</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.019771</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.017532</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.023168</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -648,25 +616,17 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -684,25 +644,17 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.028673</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.012786</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.006746</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.014102</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0.000391</v>
@@ -720,25 +672,17 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.059284</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.032557</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.024278</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.03727</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.000391</v>
@@ -756,25 +700,17 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.059284</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.032557</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-0.074652</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.498561</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-0.000391</v>
@@ -792,25 +728,17 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>-0.006249</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-0.00162</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.000467</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.008665000000000001</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -828,25 +756,17 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>-0</v>
@@ -864,25 +784,17 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
@@ -900,25 +812,17 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
@@ -936,25 +840,17 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>0.658594</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.239591</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.059937</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.56984</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-0.107396</v>
@@ -972,34 +868,26 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0.371223</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0.155203</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-0.007124</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.039972</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.100583</v>
+        <v>-0.100583</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.04954</v>
+        <v>0.04954</v>
       </c>
     </row>
     <row r="18">
@@ -1092,25 +980,17 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>0.287371</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0.084388</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.067061</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.529868</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.107396</v>
@@ -1128,25 +1008,17 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
@@ -1164,25 +1036,17 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
@@ -1200,25 +1064,17 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>0.287371</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0.084388</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.067061</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.529868</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-0.107396</v>
@@ -1236,25 +1092,17 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>0</v>
@@ -1272,25 +1120,17 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>0</v>
@@ -1350,25 +1190,17 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>0.664843</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0.241211</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.060404</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.578505</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.107396</v>
@@ -1386,25 +1218,17 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -1422,25 +1246,17 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>0.664843</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0.241211</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.060404</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.578505</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.107396</v>
@@ -1500,25 +1316,17 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>56.36598572109676</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>64.77830970278517</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-11.88581343744265</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-7.014600589639198</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -2475,10 +2283,10 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.003123</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.030167</v>
       </c>
     </row>
     <row r="65">
@@ -2559,10 +2367,10 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.018045</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.045739</v>
       </c>
     </row>
     <row r="68">
@@ -3470,25 +3278,17 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>0.287371</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>0.084388</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.067061</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.529868</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-0.107396</v>
@@ -3506,25 +3306,17 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -3542,34 +3334,26 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0.035142</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0.001274</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>-0.029611</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0.004495</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004824</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.052575</v>
       </c>
     </row>
     <row r="102">
@@ -3578,25 +3362,17 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="3" t="n">
         <v>0</v>
@@ -3614,25 +3390,17 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.004164</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>-0.00175</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.001027</v>
       </c>
       <c r="F103" s="3" t="n">
         <v>0.00084</v>
@@ -3650,25 +3418,17 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.008477</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>-0.009341</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0.061957</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.051539</v>
       </c>
       <c r="F104" s="3" t="n">
         <v>0.005434</v>
@@ -3686,25 +3446,17 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="3" t="n">
         <v>0</v>
@@ -3722,25 +3474,17 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.047783</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.008067</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-0.041516</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.198729</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>-0.070922</v>
@@ -3758,25 +3502,17 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0.02185</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="3" t="n">
         <v>0</v>
@@ -3794,25 +3530,17 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
@@ -3830,25 +3558,17 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="3" t="n">
         <v>0</v>
@@ -3866,25 +3586,17 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -3902,25 +3614,17 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -3938,25 +3642,17 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -3974,25 +3670,17 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="3" t="n">
         <v>0</v>
@@ -4010,25 +3698,17 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
         <v>0</v>
@@ -4046,34 +3726,26 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.074199</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.103204</v>
       </c>
     </row>
     <row r="116">
@@ -4082,25 +3754,17 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
@@ -4118,25 +3782,17 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="3" t="n">
         <v>0</v>
@@ -4154,25 +3810,17 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
@@ -4228,25 +3876,17 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -4264,25 +3904,17 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0</v>
@@ -4300,25 +3932,17 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="3" t="n">
         <v>0</v>
@@ -4336,25 +3960,17 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="3" t="n">
         <v>0</v>
@@ -4372,25 +3988,17 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -4408,25 +4016,17 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -4444,25 +4044,17 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="3" t="n">
         <v>0</v>
@@ -4522,25 +4114,17 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>-0.012599</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>-0.197478</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.017382</v>
       </c>
       <c r="F128" s="3" t="n">
         <v>0</v>
@@ -4558,25 +4142,17 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>0.121151</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>1.520322</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>0.239418</v>
       </c>
       <c r="F129" s="3" t="n">
         <v>0.197181</v>
@@ -4604,15 +4180,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D130" s="3" t="n">
+        <v>0.109777</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>1.295987</v>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
@@ -4632,25 +4204,17 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="3" t="n">
         <v>0</v>
@@ -4668,25 +4232,17 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0.121151</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>1.18621</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-1.245742</v>
       </c>
       <c r="F132" s="3" t="n">
         <v>-0.003228</v>
@@ -4714,15 +4270,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D133" s="3" t="n">
+        <v>1.295987</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0.050245</v>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
@@ -4742,25 +4294,17 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -4821,7 +4365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K163"/>
+  <dimension ref="A1:K243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8591,7 +8135,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -9156,7 +8704,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -9368,10 +8920,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F89" s="5" t="n">
+        <v>-0.012599</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -9418,15 +8968,11 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E90" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0.121151</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -10203,15 +9749,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G105" s="5" t="n">
+        <v>-0.041516</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>-0.198729</v>
       </c>
       <c r="I105" s="5" t="n">
         <v>-0.070922</v>
@@ -10411,15 +9953,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G109" s="5" t="n">
+        <v>1.520322</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>0.239418</v>
       </c>
       <c r="I109" s="5" t="n">
         <v>0.197181</v>
@@ -10721,15 +10259,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G115" s="5" t="n">
+        <v>1.295987</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>0.050245</v>
       </c>
       <c r="I115" s="5" t="n">
         <v>0.056412</v>
@@ -10748,20 +10282,24 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ended               Ended</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>December 31, 2025 December</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -10772,42 +10310,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G116" s="5" t="n">
+        <v>-0.067061</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>-0.529868</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J116" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="K116" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Items not involving the use of cash</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Future income tax expense (recovery)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -10821,49 +10359,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G117" s="5" t="n">
+        <v>-0.007124</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>0.039972</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J117" s="5" t="n">
-        <v>0.030915</v>
-      </c>
-      <c r="K117" s="5" t="n">
-        <v>0.07914599999999999</v>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Share-based compensation                                                       343,400)                    -)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Advertising and promotion</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Share-based compensation                                                       343,400)                    -) total</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -10874,47 +10408,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G118" s="5" t="n">
+        <v>-0.074185</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>-0.146496</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J118" s="5" t="n">
-        <v>0.085604</v>
-      </c>
-      <c r="K118" s="5" t="n">
-        <v>0.08778900000000001</v>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Changes in non-cash operating capital</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bank charges and interest</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10927,47 +10461,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G119" s="5" t="n">
+        <v>0.061957</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>-0.051539</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J119" s="5" t="n">
-        <v>0.003418</v>
-      </c>
-      <c r="K119" s="5" t="n">
-        <v>0.004509</v>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Changes in non-cash operating capital</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Amounts receivable</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10980,49 +10514,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G120" s="5" t="n">
+        <v>-0.029611</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0.004495</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J120" s="5" t="n">
-        <v>0.004741</v>
-      </c>
-      <c r="K120" s="5" t="n">
-        <v>0.008482999999999999</v>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Changes in non-cash operating capital</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Due to related parties</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -11033,47 +10563,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G121" s="5" t="n">
+        <v>0.002073</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>-0.004162</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J121" s="5" t="n">
-        <v>0.016192</v>
-      </c>
-      <c r="K121" s="5" t="n">
-        <v>0.02518</v>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Changes in non-cash operating capital</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11086,49 +10616,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G122" s="5" t="n">
+        <v>-0.00175</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>-0.001027</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J122" s="5" t="n">
-        <v>0.022715</v>
-      </c>
-      <c r="K122" s="5" t="n">
-        <v>0.104499</v>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Investing activity</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Office and administration</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Mineral property costs</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -11139,49 +10665,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G123" s="5" t="n">
+        <v>-0.292596</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>-1.286431</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J123" s="5" t="n">
-        <v>0.055645</v>
-      </c>
-      <c r="K123" s="5" t="n">
-        <v>0.076682</v>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Cash from shares issued</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -11192,47 +10714,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G124" s="5" t="n">
+        <v>1.7178</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>0.2568</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J124" s="5" t="n">
-        <v>0.016873</v>
-      </c>
-      <c r="K124" s="5" t="n">
-        <v>0.017379</v>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Salaries and benefits (Note 8)</t>
+          <t>Share issue costs</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11245,45 +10767,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G125" s="5" t="n">
+        <v>-0.197478</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>-0.017382</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J125" s="5" t="n">
-        <v>0.070974</v>
-      </c>
-      <c r="K125" s="5" t="n">
-        <v>0.10091</v>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Stock-option compensation (Notes 8 and 10)</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>(Decrease) increase in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -11294,15 +10820,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G126" s="5" t="n">
+        <v>1.18621</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>-1.245742</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -11314,27 +10836,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K126" s="5" t="n">
-        <v>0.256935</v>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Travel and accommodation</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -11345,45 +10873,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G127" s="5" t="n">
+        <v>0.109777</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>1.295987</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J127" s="5" t="n">
-        <v>0.000866</v>
-      </c>
-      <c r="K127" s="5" t="n">
-        <v>0.011592</v>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Trust and filing fees</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of the year</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -11394,49 +10926,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G128" s="5" t="n">
+        <v>1.295987</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>0.050245</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J128" s="5" t="n">
-        <v>0.021109</v>
-      </c>
-      <c r="K128" s="5" t="n">
-        <v>0.057591</v>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Cash and cash equivalents consist of</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Operating costs and expenses total</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -11447,49 +10975,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G129" s="5" t="n">
+        <v>1.28541</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>0.038531</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J129" s="5" t="n">
-        <v>0.329052</v>
-      </c>
-      <c r="K129" s="5" t="n">
-        <v>0.830695</v>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Cash and cash equivalents consist of</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Short-term deposits</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -11500,54 +11024,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G130" s="5" t="n">
+        <v>0.010577</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>0.011714</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J130" s="5" t="n">
-        <v>-0.329052</v>
-      </c>
-      <c r="K130" s="5" t="n">
-        <v>-0.830695</v>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Operator's fee income</t>
+          <t>Net income and comprehensive income for the year</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E131" s="5" t="n">
+        <v>0.287371</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>0.084388</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -11569,36 +11089,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K131" s="5" t="n">
-        <v>0.260264</v>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Adjustment for items not affecting cash</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Flow-through share premium recovery (Note 14)</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Future income tax recovery</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>-0.371223</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>-0.155203</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -11620,36 +11142,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K132" s="5" t="n">
-        <v>0.110096</v>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Adjustment for items not affecting cash</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Part XII.6 tax</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F133" s="5" t="n">
+        <v>0.02185</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -11666,8 +11192,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J133" s="5" t="n">
-        <v>-0.002268</v>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -11678,33 +11206,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Adjustment for items not affecting cash</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Adjustment for items not affecting cash total</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" s="5" t="n">
+        <v>-0.083852</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>-0.048965</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -11721,39 +11241,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J134" s="5" t="n">
-        <v>-0.000867</v>
-      </c>
-      <c r="K134" s="5" t="n">
-        <v>-0.001804</v>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Changes in non-cash working capital components</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dividend income net of withholding tax</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GST receivable</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>0.035142</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>0.001274</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -11770,38 +11294,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J135" s="5" t="n">
-        <v>0.000595</v>
-      </c>
-      <c r="K135" s="5" t="n">
-        <v>0.000109</v>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Changes in non-cash working capital components</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0.004164</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11823,43 +11349,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J136" s="5" t="n">
-        <v>0.015777</v>
-      </c>
-      <c r="K136" s="5" t="n">
-        <v>0.028036</v>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Changes in non-cash working capital components</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>0.008477</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>-0.009341</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -11876,39 +11402,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J137" s="5" t="n">
-        <v>-0.315815</v>
-      </c>
-      <c r="K137" s="5" t="n">
-        <v>-0.433994</v>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Changes in non-cash working capital components</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (expense) (Note 13)</t>
+          <t>Due to related parties</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E138" s="5" t="n">
+        <v>0.011891</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>-0.006265</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -11925,43 +11451,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J138" s="5" t="n">
-        <v>0.100583</v>
-      </c>
-      <c r="K138" s="5" t="n">
-        <v>-0.04954</v>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Changes in non-cash working capital components</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Changes in non-cash working capital components total</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="5" t="n">
+        <v>-0.024178</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>-0.06329700000000001</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -11978,39 +11500,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J139" s="5" t="n">
-        <v>-0.215232</v>
-      </c>
-      <c r="K139" s="5" t="n">
-        <v>-0.483534</v>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>reclassified subsequently to profit or loss</t>
+          <t>Investing Activity</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Realized gain on sale of marketable securities</t>
+          <t>Mineral property costs</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E140" s="5" t="n">
+        <v>-0.107927</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>-0.027365</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -12027,27 +11549,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J140" s="5" t="n">
-        <v>0.004021</v>
-      </c>
-      <c r="K140" s="5" t="n">
-        <v>0.042308</v>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>reclassified subsequently to profit or loss</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Net change in fair value of marketable securities</t>
+          <t>Cash from shares issued</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -12056,10 +11582,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F141" s="5" t="n">
+        <v>0.13375</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -12076,34 +11600,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J141" s="5" t="n">
-        <v>-0.061475</v>
-      </c>
-      <c r="K141" s="5" t="n">
-        <v>0.077872</v>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>reclassified subsequently to profit or loss</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>reclassified subsequently to profit or loss total</t>
+          <t>Cash from shares to be issued</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E142" s="5" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12125,43 +11651,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J142" s="5" t="n">
-        <v>-0.057454</v>
-      </c>
-      <c r="K142" s="5" t="n">
-        <v>0.12018</v>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>reclassified subsequently to profit or loss</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash provided (used) during the year</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" s="5" t="n">
+        <v>-0.062105</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.030489</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -12178,43 +11700,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J143" s="5" t="n">
-        <v>-0.272686</v>
-      </c>
-      <c r="K143" s="5" t="n">
-        <v>-0.363354</v>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>reclassified subsequently to profit or loss</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and short-term deposits - beginning of year</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" s="5" t="n">
+        <v>0.141393</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>0.079288</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -12231,43 +11749,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J144" s="5" t="n">
-        <v>138.286095</v>
-      </c>
-      <c r="K144" s="5" t="n">
-        <v>152.937779</v>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>reclassified subsequently to profit or loss</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and short-term deposits - end of year</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" s="5" t="n">
+        <v>0.079288</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>0.109777</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -12284,34 +11798,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" s="5" t="n">
-        <v>0</v>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Atty and Pil Claims</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Advertising and promotion 5,382)</t>
+          <t>Acquisition 73,220 - 73,220</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E146" s="5" t="n">
+        <v>0.07321999999999999</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12328,8 +11844,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I146" s="5" t="n">
-        <v>0.001718</v>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -12345,28 +11863,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Atty and Pil Claims</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bank charges and interest 317)</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Assay, IP and linecutting 528,106 408 528,514</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" s="5" t="n">
+        <v>0.528514</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12383,8 +11895,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="5" t="n">
-        <v>0.000391</v>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -12400,24 +11914,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Atty and Pil Claims</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Insurance 3,927)</t>
+          <t>Camp accommodation and travel 1,020,059 - 1,020,059</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E148" s="5" t="n">
+        <v>1.020059</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12434,8 +11946,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I148" s="5" t="n">
-        <v>0.003927</v>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -12451,24 +11965,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Atty and Pil Claims</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Legal and accounting 15,805)</t>
+          <t>Drilling 1,466,687 - 1,466,687</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E149" s="5" t="n">
+        <v>1.466687</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12485,8 +11997,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="5" t="n">
-        <v>0.019195</v>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -12502,24 +12016,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Atty and Pil Claims</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Office and administration 8,791)</t>
+          <t>Equipment rental 129,613 - 129,613</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E150" s="5" t="n">
+        <v>0.129613</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12536,8 +12048,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I150" s="5" t="n">
-        <v>0.008016000000000001</v>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -12553,29 +12067,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Atty and Pil Claims</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Rent 11,508)</t>
+          <t>Field office 115,318 931 116,249</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E151" s="5" t="n">
+        <v>0.118409</v>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>0.00216</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -12587,8 +12097,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="5" t="n">
-        <v>0.011107</v>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -12604,24 +12116,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Atty and Pil Claims</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Shareholder relations 79)</t>
+          <t>Geological and geophysical 1,444,246 5,808 1,450,054</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E152" s="5" t="n">
+        <v>1.450054</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12638,8 +12148,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I152" s="5" t="n">
-        <v>0.007145</v>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -12655,24 +12167,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Atty and Pil Claims</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Telephone 878)</t>
+          <t>Road construction 392,273 - 392,273</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E153" s="5" t="n">
+        <v>0.392273</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12689,8 +12199,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="5" t="n">
-        <v>0.000793</v>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -12706,29 +12218,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Atty and Pil Claims</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Travel and accommodation 1,858)</t>
+          <t>Atty and Pil Claims total</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E154" s="5" t="n">
+        <v>5.178829</v>
+      </c>
+      <c r="F154" s="5" t="n">
+        <v>0.00216</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -12740,8 +12248,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I154" s="5" t="n">
-        <v>0.004662</v>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -12757,29 +12267,25 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Silver Hope Claims</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Trust and filing fees 14,632)</t>
+          <t>Acquisition 173,928 2,406 176,334</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E155" s="5" t="n">
+        <v>0.180352</v>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>0.004018</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -12791,8 +12297,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="5" t="n">
-        <v>0.016861</v>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -12808,29 +12316,25 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Silver Hope Claims</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Loss before other items (63,177)</t>
+          <t>Assay, IP and linecutting 72,528 82,653 155,181</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E156" s="5" t="n">
+        <v>0.161798</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>0.006617</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -12842,8 +12346,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I156" s="5" t="n">
-        <v>-0.07381500000000001</v>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -12859,29 +12365,25 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Silver Hope Claims</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Interest income 309)</t>
+          <t>Camp accommodation and travel 15,236 2,884 18,120</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E157" s="5" t="n">
+        <v>0.020761</v>
+      </c>
+      <c r="F157" s="5" t="n">
+        <v>0.002641</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -12893,8 +12395,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="5" t="n">
-        <v>0.000806</v>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -12910,24 +12414,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Silver Hope Claims</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Flow-through share premium 29,167)</t>
+          <t>Drilling 230,428 - 230,428</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E158" s="5" t="n">
+        <v>0.230428</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12944,8 +12446,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I158" s="5" t="n">
-        <v>0.02524</v>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -12961,24 +12465,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Silver Hope Claims</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Loss before income taxes (33,701)</t>
+          <t>Equipment rental 3,233 - 3,233</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E159" s="5" t="n">
+        <v>0.003233</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12995,8 +12497,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="5" t="n">
-        <v>-0.047769</v>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -13012,29 +12516,25 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Silver Hope Claims</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (72,858)</t>
+          <t>Field office - - -</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E160" s="5" t="n">
+        <v>0.000811</v>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>0.000811</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -13046,8 +12546,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I160" s="5" t="n">
-        <v>-0.059627</v>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -13063,33 +12565,25 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Silver Hope Claims</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year (106,559)</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Geological and geophysical 80,998 25,805 106,803</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" s="5" t="n">
+        <v>0.108293</v>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>0.00149</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -13101,8 +12595,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="5" t="n">
-        <v>-0.107396</v>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -13118,28 +12614,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Silver Hope Claims</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding 58,810,216</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Road construction 18,876 - 18,876</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" s="5" t="n">
+        <v>0.018876</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13156,8 +12646,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I162" s="5" t="n">
-        <v>55.170993</v>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -13173,53 +12665,4187 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Silver Hope Claims</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Silver Hope Claims total</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" s="5" t="n">
+        <v>0.724552</v>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>0.015577</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Silver Hope Claims</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Total Deferred Mineral Property Costs 5,764,749 120,895 5,885,644</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" s="5" t="n">
+        <v>5.903381</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>0.017737</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Ended               Ended</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>December 31, 2025 December</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
         <is>
           <t>Operating costs and expenses</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="n">
+        <v>0.030915</v>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>0.07914599999999999</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Advertising and promotion</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.005273</v>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>0.007055</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" s="5" t="n">
+        <v>0.085604</v>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>0.08778900000000001</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Bank charges and interest</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.000613</v>
+      </c>
+      <c r="H168" s="5" t="n">
+        <v>0.006093</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J168" s="5" t="n">
+        <v>0.003418</v>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>0.004509</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="5" t="n">
+        <v>0.004741</v>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>0.008482999999999999</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" s="5" t="n">
+        <v>0.016192</v>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>0.02518</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="5" t="n">
+        <v>0.022715</v>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>0.104499</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Office and administration</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" s="5" t="n">
+        <v>0.055645</v>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>0.076682</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="5" t="n">
+        <v>0.016873</v>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>0.017379</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Salaries and benefits (Note 8)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J174" s="5" t="n">
+        <v>0.070974</v>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>0.10091</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Stock-option compensation (Notes 8 and 10)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>0.256935</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Travel and accommodation</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" s="5" t="n">
+        <v>0.000866</v>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>0.011592</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Trust and filing fees</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="5" t="n">
+        <v>0.021109</v>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>0.057591</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses total</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" s="5" t="n">
+        <v>0.329052</v>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>0.830695</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="5" t="n">
+        <v>-0.329052</v>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>-0.830695</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Operator's fee income</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>0.260264</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Flow-through share premium recovery (Note 14)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>0.110096</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Part XII.6 tax</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" s="5" t="n">
+        <v>-0.002268</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="5" t="n">
+        <v>-0.000867</v>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>-0.001804</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Dividend income net of withholding tax</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" s="5" t="n">
+        <v>0.000595</v>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>0.000109</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" s="5" t="n">
+        <v>0.015777</v>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>0.028036</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" s="5" t="n">
+        <v>-0.315815</v>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>-0.433994</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Deferred income tax recovery (expense) (Note 13)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J187" s="5" t="n">
+        <v>0.100583</v>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>-0.04954</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J188" s="5" t="n">
+        <v>-0.215232</v>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>-0.483534</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>reclassified subsequently to profit or loss</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Realized gain on sale of marketable securities</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" s="5" t="n">
+        <v>0.004021</v>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>0.042308</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>reclassified subsequently to profit or loss</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Net change in fair value of marketable securities</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J190" s="5" t="n">
+        <v>-0.061475</v>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>0.077872</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>reclassified subsequently to profit or loss</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>reclassified subsequently to profit or loss total</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J191" s="5" t="n">
+        <v>-0.057454</v>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>0.12018</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>reclassified subsequently to profit or loss</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J192" s="5" t="n">
+        <v>-0.272686</v>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>-0.363354</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>reclassified subsequently to profit or loss</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J193" s="5" t="n">
+        <v>138.286095</v>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>152.937779</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>reclassified subsequently to profit or loss</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J194" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Advertising and promotion 5,382)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" s="5" t="n">
+        <v>0.001718</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Bank charges and interest 317)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" s="5" t="n">
+        <v>0.000391</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Insurance 3,927)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" s="5" t="n">
+        <v>0.003927</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Legal and accounting 15,805)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I198" s="5" t="n">
+        <v>0.019195</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Office and administration 8,791)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" s="5" t="n">
+        <v>0.008016000000000001</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Rent 11,508)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" s="5" t="n">
+        <v>0.011107</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Shareholder relations 79)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" s="5" t="n">
+        <v>0.007145</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Telephone 878)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>0.000793</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Travel and accommodation 1,858)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" s="5" t="n">
+        <v>0.004662</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Trust and filing fees 14,632)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>0.016861</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Loss before other items (63,177)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" s="5" t="n">
+        <v>-0.07381500000000001</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Interest income 309)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" s="5" t="n">
+        <v>0.000806</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Flow-through share premium 29,167)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" s="5" t="n">
+        <v>0.02524</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Loss before income taxes (33,701)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" s="5" t="n">
+        <v>-0.047769</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Deferred income tax expense (72,858)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>-0.059627</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year (106,559)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>-0.107396</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding 58,810,216</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>55.170993</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Operating costs and expenses</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
         <is>
           <t>Basic and diluted loss per share (0.00) $</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I163" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Consulting                                                                                                    -)            4,900)</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="n">
+        <v>0.00175</v>
+      </c>
+      <c r="H213" s="5" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Consulting                                                                                                    -)            4,900)</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Legal and accounting</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="n">
+        <v>0.023797</v>
+      </c>
+      <c r="H214" s="5" t="n">
+        <v>0.033596</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Consulting                                                                                                    -)            4,900)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Office and administration</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="n">
+        <v>0.006406</v>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>0.009535999999999999</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Consulting                                                                                                    -)            4,900)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="n">
+        <v>0.009376000000000001</v>
+      </c>
+      <c r="H216" s="5" t="n">
+        <v>0.010732</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Share-based compensation                                                     343,400)                     -)</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Telephone</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="n">
+        <v>0.00086</v>
+      </c>
+      <c r="H217" s="5" t="n">
+        <v>0.000954</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Share-based compensation                                                     343,400)                     -)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Travel and accommodation</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G218" s="5" t="n">
+        <v>0.005948</v>
+      </c>
+      <c r="H218" s="5" t="n">
+        <v>0.008451999999999999</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Share-based compensation                                                     343,400)                     -)</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Trust and filing fees</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="n">
+        <v>0.015729</v>
+      </c>
+      <c r="H219" s="5" t="n">
+        <v>0.012599</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Share-based compensation                                                     343,400)                     -)</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Loss before other item</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" s="5" t="n">
+        <v>-0.074652</v>
+      </c>
+      <c r="H220" s="5" t="n">
+        <v>-0.498561</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Share-based compensation                                                     343,400)                     -)</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G221" s="5" t="n">
+        <v>0.000467</v>
+      </c>
+      <c r="H221" s="5" t="n">
+        <v>0.008665000000000001</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Share-based compensation                                                     343,400)                     -)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Loss before taxes</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G222" s="5" t="n">
+        <v>-0.074185</v>
+      </c>
+      <c r="H222" s="5" t="n">
+        <v>-0.489896</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Share-based compensation                                                     343,400)                     -)</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Future income tax (expense) recovery</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>0.007124</v>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>-0.039972</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Share-based compensation                                                     343,400)                     -)</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="n">
+        <v>-0.067061</v>
+      </c>
+      <c r="H224" s="5" t="n">
+        <v>-0.529868</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Share-based compensation                                                     343,400)                     -)</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="n">
+        <v>43.551003</v>
+      </c>
+      <c r="H225" s="5" t="n">
+        <v>50.417518</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Share-based compensation                                                     343,400)                     -)</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="n">
+        <v>0.013418</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Filing and transfer agent</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="n">
+        <v>0.015255</v>
+      </c>
+      <c r="F228" s="5" t="n">
+        <v>0.012786</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Interest and bank charges</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="n">
+        <v>0.00384</v>
+      </c>
+      <c r="F229" s="5" t="n">
+        <v>0.000329</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="n">
+        <v>-0.006249</v>
+      </c>
+      <c r="F230" s="5" t="n">
+        <v>-0.00162</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Office and miscellaneous</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="n">
+        <v>0.006889</v>
+      </c>
+      <c r="F231" s="5" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="n">
+        <v>0.030817</v>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>0.018028</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="n">
+        <v>0.009427</v>
+      </c>
+      <c r="F233" s="5" t="n">
+        <v>0.010334</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Shareholder communication</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="n">
+        <v>0.000849</v>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>0.000833</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="n">
+        <v>0.02185</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="n">
+        <v>0.009606</v>
+      </c>
+      <c r="F236" s="5" t="n">
+        <v>0.004975</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year before tax</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" s="5" t="n">
+        <v>-0.083852</v>
+      </c>
+      <c r="F237" s="5" t="n">
+        <v>-0.070815</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Future income tax recovery</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E238" s="5" t="n">
+        <v>0.371223</v>
+      </c>
+      <c r="F238" s="5" t="n">
+        <v>0.155203</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Net income and comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E239" s="5" t="n">
+        <v>0.287371</v>
+      </c>
+      <c r="F239" s="5" t="n">
+        <v>0.084388</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Deficit - beginning of year</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" s="5" t="n">
+        <v>-0.7776420000000001</v>
+      </c>
+      <c r="F240" s="5" t="n">
+        <v>-0.490271</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Deficit - end of year</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" s="5" t="n">
+        <v>-0.490271</v>
+      </c>
+      <c r="F241" s="5" t="n">
+        <v>-0.405883</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Basic and diluted earnings per share $</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E242" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="F242" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Basic and diluted weighted-average number of common shares</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Basic and diluted weighted-average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="n">
+        <v>37.655907</v>
+      </c>
+      <c r="F243" s="5" t="n">
+        <v>39.799469</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
         <is>
           <t>-</t>
         </is>
